--- a/public/data/contract_age.xlsx
+++ b/public/data/contract_age.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>f64fb432-28fe-4fc9-b6de-0dabc8a85553</v>
+        <v>c7acfe7c-8893-4903-b540-968a4ab89519</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D2" t="str">
         <v>CTR-001-001</v>
@@ -447,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>5557f527-98ef-4fbb-b94d-079674501e43</v>
+        <v>d36f53dd-20ed-4f97-a407-df450e8cd48f</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D3" t="str">
         <v>CTR-001-001</v>
@@ -470,16 +470,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>122fef6e-b0cc-4110-9303-7428c3c531a7</v>
+        <v>a5345232-5c81-4c0e-832c-72bd10ca6330</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D4" t="str">
-        <v>CTR-002-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="E4" t="str">
         <v>Adult</v>
@@ -493,16 +493,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>cf26d501-8014-495f-a630-c7b722743daa</v>
+        <v>59c2af63-2444-4f6b-9cd3-f5c5e6b32112</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D5" t="str">
-        <v>CTR-002-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="E5" t="str">
         <v>Child</v>
@@ -516,16 +516,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>7c63ea1d-4941-4b08-b36d-df51799ab168</v>
+        <v>fc9e72f0-9ad9-46be-8113-75fc3c463c18</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D6" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="E6" t="str">
         <v>Adult</v>
@@ -539,16 +539,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>3d5719c6-053e-4fb7-a946-ebe012c54722</v>
+        <v>8b999cda-ddc3-4168-aed9-d2912caf27c3</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D7" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="E7" t="str">
         <v>Child</v>
@@ -562,16 +562,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>5d8503d7-053d-4457-ab8b-f2fe1b4d5ca0</v>
+        <v>7196a4be-1cb3-4146-80e6-e9aae903d25b</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D8" t="str">
-        <v>CTR-005-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E8" t="str">
         <v>Adult</v>
@@ -585,16 +585,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>3b969c05-b3a3-4c86-bc69-a13dc0e5fb2e</v>
+        <v>eef18aef-59e6-45db-8927-f5d6b8ad17b9</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D9" t="str">
-        <v>CTR-005-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E9" t="str">
         <v>Child</v>
@@ -608,16 +608,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2eeda8ec-6a91-4068-ab52-65b5c26605d1</v>
+        <v>3b134594-b7cc-4d61-b8c2-1766635d71c3</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D10" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-002</v>
       </c>
       <c r="E10" t="str">
         <v>Adult</v>
@@ -631,16 +631,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>f0d7f5d2-0d3e-4e75-b7f4-d68896b43676</v>
+        <v>c4fb038a-7e04-417b-9c05-148de6c966ee</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D11" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-002</v>
       </c>
       <c r="E11" t="str">
         <v>Child</v>
@@ -654,22 +654,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>cb881ce9-bcec-4651-94bb-c99bbbcaab32</v>
+        <v>9719d4cd-85ce-4f54-9837-69b4c8d2865c</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D12" t="str">
-        <v>CTR-007-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="E12" t="str">
         <v>Adult</v>
       </c>
       <c r="F12">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -677,16 +677,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>b5278326-7d0a-4fed-aed2-039f3abaad25</v>
+        <v>3e6ba279-841d-445e-ad66-ec0d75a795b6</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D13" t="str">
-        <v>CTR-007-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="E13" t="str">
         <v>Child</v>
@@ -695,21 +695,21 @@
         <v>2</v>
       </c>
       <c r="G13">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>e592a790-32fd-4a62-a395-c17cec7bf1c4</v>
+        <v>8ee1c0af-079e-47f8-8051-351074285431</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D14" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-004-001</v>
       </c>
       <c r="E14" t="str">
         <v>Adult</v>
@@ -723,16 +723,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>b579b992-14db-4173-9db4-8a9895c9eaea</v>
+        <v>56e29561-bcf6-461a-b5ad-2da0a1b48e62</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C15" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D15" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-004-001</v>
       </c>
       <c r="E15" t="str">
         <v>Child</v>
@@ -746,16 +746,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>b29043a4-a125-42a4-986c-ed774e96a2a8</v>
+        <v>2755a0e4-66c5-4aca-ad1e-59525be5e2da</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C16" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D16" t="str">
-        <v>CTR-009-001</v>
+        <v>CTR-005-001</v>
       </c>
       <c r="E16" t="str">
         <v>Adult</v>
@@ -769,16 +769,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>a2727d16-fbb8-4d63-a7ac-f895c17f5b06</v>
+        <v>b85c5289-9cf3-4d7b-aac4-18929d6d168f</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C17" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D17" t="str">
-        <v>CTR-009-001</v>
+        <v>CTR-005-001</v>
       </c>
       <c r="E17" t="str">
         <v>Child</v>
@@ -792,16 +792,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>440fd302-08a3-49e7-a967-5dc19ccb15a8</v>
+        <v>86e392f1-3616-41e2-b1a9-1953abf97ea3</v>
       </c>
       <c r="B18" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C18" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D18" t="str">
-        <v>CTR-010-001</v>
+        <v>CTR-005-002</v>
       </c>
       <c r="E18" t="str">
         <v>Adult</v>
@@ -815,30 +815,490 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>8ccfeff5-d76e-45c7-bbe4-bbb50ca918b9</v>
+        <v>54e24af4-3791-4056-8f22-c052c5465336</v>
       </c>
       <c r="B19" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C19" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D19" t="str">
+        <v>CTR-005-002</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Child</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>9bfae15c-66d7-4b8e-996f-c871654272ee</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D20" t="str">
+        <v>CTR-006-001</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="F20">
+        <v>12</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>74284e75-7a36-4f8d-9844-a04551184e4b</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D21" t="str">
+        <v>CTR-006-001</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Child</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>45b07b4c-34d2-429c-a7d6-e7a9ed632548</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D22" t="str">
+        <v>CTR-006-002</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="F22">
+        <v>12</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>d21ce1ae-0512-4aad-8a05-d8602b6897ab</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D23" t="str">
+        <v>CTR-006-002</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Child</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>9cfd86b3-29f4-4677-b914-c03b384689cc</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D24" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="F24">
+        <v>12</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>0ee24022-3c5a-4021-a691-ad42da368337</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C25" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D25" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Child</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>1dc9e3d1-d427-400f-a3c0-65b0b9942c86</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C26" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D26" t="str">
+        <v>CTR-007-001</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="F26">
+        <v>13</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>e5c192ca-eb15-4a24-94ef-93c12fae420b</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C27" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D27" t="str">
+        <v>CTR-007-001</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Child</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>c6c40f0c-1c30-48e1-a4a7-301455e74c94</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C28" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D28" t="str">
+        <v>CTR-007-002</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="F28">
+        <v>13</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>f156f758-7455-4bf1-ae30-f0b1cde6e3a7</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C29" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D29" t="str">
+        <v>CTR-007-002</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Child</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>4e4dbe7b-c72f-43f5-8f67-23c5172966fa</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C30" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D30" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="F30">
+        <v>12</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>f725a8c8-d6d1-4c6d-bf89-1007bd7b578a</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C31" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D31" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Child</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>d01141e2-e9ff-4069-8428-d1858056beb7</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C32" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D32" t="str">
+        <v>CTR-008-002</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="F32">
+        <v>12</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>dc93633b-e976-4ed5-b780-cc33c4c160d1</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C33" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D33" t="str">
+        <v>CTR-008-002</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Child</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>33f280c9-fcc2-4e80-8bd7-4112cf190732</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C34" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D34" t="str">
+        <v>CTR-009-001</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="F34">
+        <v>12</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>83f6a2d6-37f1-434a-884a-28e8c0b495f8</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C35" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D35" t="str">
+        <v>CTR-009-001</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Child</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="G35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>1a17d5c3-0a52-4f5f-8f29-88d35e90d352</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C36" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D36" t="str">
         <v>CTR-010-001</v>
       </c>
-      <c r="E19" t="str">
-        <v>Child</v>
-      </c>
-      <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19">
+      <c r="E36" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="F36">
+        <v>12</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>877f8af8-5fb9-432a-93e0-6c5966da4bad</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C37" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D37" t="str">
+        <v>CTR-010-001</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Child</v>
+      </c>
+      <c r="F37">
+        <v>2</v>
+      </c>
+      <c r="G37">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>cbce127f-0a7b-4bf2-a9d4-ad5d71109534</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C38" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D38" t="str">
+        <v>CTR-010-002</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Adult</v>
+      </c>
+      <c r="F38">
+        <v>12</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>7a8f4f12-fab9-4c94-8281-3362134ce14c</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C39" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D39" t="str">
+        <v>CTR-010-002</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Child</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G39"/>
   </ignoredErrors>
 </worksheet>
 </file>